--- a/reports/Debug-snowbowl-20260106/For The Day (Actual)_Budget.xlsx
+++ b/reports/Debug-snowbowl-20260106/For The Day (Actual)_Budget.xlsx
@@ -46,6 +46,75 @@
     <t>D6215</t>
   </si>
   <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4032</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5112</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>99100</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
     <t>99150</t>
   </si>
   <si>
@@ -67,75 +136,6 @@
     <t>D8040</t>
   </si>
   <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5112</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4032</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
-    <t>99100</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -181,6 +181,75 @@
     <t>Housekeeping</t>
   </si>
   <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>Hart Prairie Retail</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>Hart Prairie Restaurant</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
+    <t>Rental Repair Shop</t>
+  </si>
+  <si>
+    <t>Agassiz Restaurant</t>
+  </si>
+  <si>
+    <t>Base Camp Restaurant</t>
+  </si>
+  <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>Agassiz Retail</t>
+  </si>
+  <si>
+    <t>Fort Valley Lodge</t>
+  </si>
+  <si>
+    <t>Fremont Restaurant</t>
+  </si>
+  <si>
+    <t>Janitorial</t>
+  </si>
+  <si>
+    <t>Daily Winter Ticketed</t>
+  </si>
+  <si>
+    <t>Ski School</t>
+  </si>
+  <si>
+    <t>Rentals</t>
+  </si>
+  <si>
+    <t>Base Camp Hotel</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
     <t>Comp Tickets</t>
   </si>
   <si>
@@ -200,75 +269,6 @@
   </si>
   <si>
     <t>HR</t>
-  </si>
-  <si>
-    <t>Rental Repair Shop</t>
-  </si>
-  <si>
-    <t>Agassiz Restaurant</t>
-  </si>
-  <si>
-    <t>Base Camp Restaurant</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
-  </si>
-  <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>Hart Prairie Retail</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>Hart Prairie Restaurant</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>Agassiz Retail</t>
-  </si>
-  <si>
-    <t>Fort Valley Lodge</t>
-  </si>
-  <si>
-    <t>Fremont Restaurant</t>
-  </si>
-  <si>
-    <t>Janitorial</t>
-  </si>
-  <si>
-    <t>Daily Winter Ticketed</t>
-  </si>
-  <si>
-    <t>Ski School</t>
-  </si>
-  <si>
-    <t>Rentals</t>
-  </si>
-  <si>
-    <t>Base Camp Hotel</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Accounting</t>
   </si>
 </sst>
 </file>
@@ -799,10 +799,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2">
-        <v>150.00</v>
+        <v>911.72</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>55</v>
@@ -816,7 +816,7 @@
         <v>41</v>
       </c>
       <c r="C13" s="2">
-        <v>1140.00</v>
+        <v>468.05</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>56</v>
@@ -824,44 +824,44 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2">
-        <v>913.71</v>
+        <v>12286.70</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="2">
-        <v>589.33</v>
+        <v>250.06</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C16" s="2">
-        <v>771.74</v>
+        <v>572.10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -869,10 +869,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2">
-        <v>0.00</v>
+        <v>581.37</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>59</v>
@@ -883,10 +883,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2">
-        <v>846.78</v>
+        <v>650.00</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>60</v>
@@ -900,7 +900,7 @@
         <v>41</v>
       </c>
       <c r="C19" s="2">
-        <v>410.80</v>
+        <v>2597.04</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>61</v>
@@ -908,16 +908,16 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2">
-        <v>324.00</v>
+        <v>16399.88</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -925,10 +925,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2">
-        <v>867.00</v>
+        <v>144.38</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>62</v>
@@ -942,7 +942,7 @@
         <v>41</v>
       </c>
       <c r="C22" s="2">
-        <v>908.27</v>
+        <v>324.00</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>63</v>
@@ -956,7 +956,7 @@
         <v>42</v>
       </c>
       <c r="C23" s="2">
-        <v>8586.00</v>
+        <v>867.00</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>63</v>
@@ -970,7 +970,7 @@
         <v>41</v>
       </c>
       <c r="C24" s="2">
-        <v>301.30</v>
+        <v>908.27</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>64</v>
@@ -984,7 +984,7 @@
         <v>42</v>
       </c>
       <c r="C25" s="2">
-        <v>1092.42</v>
+        <v>8586.00</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>64</v>
@@ -998,7 +998,7 @@
         <v>41</v>
       </c>
       <c r="C26" s="2">
-        <v>308.50</v>
+        <v>301.30</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>65</v>
@@ -1006,30 +1006,30 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2">
-        <v>911.72</v>
+        <v>1092.42</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C28" s="2">
-        <v>468.05</v>
+        <v>308.50</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1037,10 +1037,10 @@
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2">
-        <v>12286.70</v>
+        <v>2725.11</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>67</v>
@@ -1051,10 +1051,10 @@
         <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2">
-        <v>250.06</v>
+        <v>756.62</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>68</v>
@@ -1062,254 +1062,254 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="2">
-        <v>572.10</v>
+        <v>182.16</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="2">
-        <v>581.37</v>
+        <v>215.86</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C33" s="2">
-        <v>650.00</v>
+        <v>270.38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="2">
-        <v>2597.04</v>
+        <v>557.02</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="2">
-        <v>16399.88</v>
+        <v>2999.25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C36" s="2">
-        <v>144.38</v>
+        <v>637.57</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" s="2">
-        <v>2725.11</v>
+        <v>1450.00</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="2">
-        <v>756.62</v>
+        <v>3577.79</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" s="2">
-        <v>182.16</v>
+        <v>10002.00</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C40" s="2">
-        <v>215.86</v>
+        <v>23531.00</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C41" s="2">
-        <v>270.38</v>
+        <v>2211.50</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C42" s="2">
-        <v>557.02</v>
+        <v>644.84</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="2">
-        <v>2999.25</v>
+        <v>2832.65</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C44" s="2">
-        <v>637.57</v>
+        <v>587.05</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C45" s="2">
-        <v>1450.00</v>
+        <v>980.31</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C46" s="2">
-        <v>3577.79</v>
+        <v>150.00</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="2">
-        <v>10002.00</v>
+        <v>1140.00</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="2">
-        <v>23531.00</v>
+        <v>913.71</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="C49" s="2">
-        <v>2211.50</v>
+        <v>589.33</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>81</v>
@@ -1334,7 +1334,7 @@
         <v>41</v>
       </c>
       <c r="C50" s="2">
-        <v>644.84</v>
+        <v>771.74</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>82</v>
@@ -1348,7 +1348,7 @@
         <v>42</v>
       </c>
       <c r="C51" s="2">
-        <v>2832.65</v>
+        <v>0.00</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>82</v>
@@ -1362,7 +1362,7 @@
         <v>41</v>
       </c>
       <c r="C52" s="2">
-        <v>587.05</v>
+        <v>846.78</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>83</v>
@@ -1376,7 +1376,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="2">
-        <v>980.31</v>
+        <v>410.80</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>84</v>
